--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3D19C0-7915-464A-9465-094389212614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2090DA49-DB43-4C71-9B53-A6B916307B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>날짜</t>
   </si>
@@ -222,6 +222,26 @@
   </si>
   <si>
     <t>GRIN 50</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>P100+</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>250기본</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>200/220MMF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20/400 BC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>200W 지날때 53도 (너무 높음)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -307,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -319,6 +339,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -621,23 +642,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="4.375" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="3.625" customWidth="1"/>
+    <col min="9" max="9" width="4.625" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="23.875" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -695,55 +716,78 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7">
+        <v>46305</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2">
+        <v>200</v>
+      </c>
+      <c r="P2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
         <v>-100</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K3" s="2">
         <v>-1000</v>
       </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2">
-        <v>0</v>
-      </c>
-      <c r="O2" s="2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6" t="s">
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+      <c r="O3" s="2">
+        <v>0</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6" t="s">
         <v>46</v>
       </c>
     </row>

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2090DA49-DB43-4C71-9B53-A6B916307B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD44C691-ECCE-476A-BDB2-72DAD62AA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
     <sheet name="Cleaver" sheetId="2" r:id="rId2"/>
-    <sheet name="작성 안내" sheetId="3" r:id="rId3"/>
+    <sheet name="NA Measure" sheetId="4" r:id="rId3"/>
+    <sheet name="작성 안내" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>날짜</t>
   </si>
@@ -244,12 +245,86 @@
     <t>200W 지날때 53도 (너무 높음)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>00/220 MMF</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA(measured)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA(Spec sheet)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fiber</t>
+  </si>
+  <si>
+    <r>
+      <t>x1,2 y1,2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기하적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계산</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,8 +376,16 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,8 +397,14 @@
         <fgColor rgb="FFE8F5F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -323,11 +412,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -339,7 +437,21 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -662,7 +774,7 @@
     <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="60.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -897,6 +1009,79 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F6C447-90B8-47E1-98D9-F18C40565832}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="30.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD44C691-ECCE-476A-BDB2-72DAD62AA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904DADFB-84FC-48B2-BCB5-9200E872A196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="2880" windowWidth="21750" windowHeight="14790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
   <si>
     <t>날짜</t>
   </si>
@@ -246,24 +246,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>00/220 MMF</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA(measured)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>NA(Spec sheet)</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -271,9 +253,14 @@
     <t>Fiber</t>
   </si>
   <si>
-    <r>
-      <t>x1,2 y1,2</t>
-    </r>
+    <t>x</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulated</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -281,7 +268,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>로</t>
+      <t>그외</t>
     </r>
     <r>
       <rPr>
@@ -298,7 +285,7 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t>기하적으로</t>
+      <t>발산</t>
     </r>
     <r>
       <rPr>
@@ -315,8 +302,177 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
+      <t>큰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스펙클도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>관찰</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Divergence Angle (msrd)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA (msrd)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">x1, y1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기하적으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
       <t>계산</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>at red</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>at 976</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMF28</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번호</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비고</t>
+    </r>
+  </si>
+  <si>
+    <t>200/220 MMF</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비고</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMF28+NCF 1mm</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMF+NCF+Grin(50) 1+1mm</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고차모드와 근본모드 나뉨</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -324,7 +480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +540,26 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -404,7 +580,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -421,11 +597,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -446,11 +633,61 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1010,33 +1247,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F6C447-90B8-47E1-98D9-F18C40565832}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="1" max="1" width="4.625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="11.125" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17" s="12" customFormat="1" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="H1" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>67</v>
+      </c>
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
       <c r="L1" s="9"/>
@@ -1046,38 +1297,156 @@
       <c r="P1" s="9"/>
       <c r="Q1" s="9"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="C2" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="18">
         <v>0.22</v>
       </c>
-      <c r="D2" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="16">
+        <v>9.9700000000000006</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.17299999999999999</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="19"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="22">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23">
+        <v>46308</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="6"/>
+      <c r="I3" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="22">
+        <v>2</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="25">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E4" s="24">
+        <v>6.56</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0.11</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="28">
+        <v>3</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="12">
+        <v>5.14</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.09</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" s="13"/>
+      <c r="H6"/>
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B7" s="13"/>
+      <c r="H7"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B8" s="13"/>
+      <c r="H8"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B9" s="13"/>
+      <c r="H9"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B10" s="13"/>
+      <c r="H10"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11" s="13"/>
+      <c r="H11"/>
+      <c r="I11" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904DADFB-84FC-48B2-BCB5-9200E872A196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7798BDEB-3987-4AB4-AA9D-798FE40B0CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="2880" windowWidth="21750" windowHeight="14790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="810" windowWidth="21750" windowHeight="14790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
   <si>
     <t>날짜</t>
   </si>
@@ -473,6 +473,14 @@
   </si>
   <si>
     <t>고차모드와 근본모드 나뉨</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">angles &lt;0.4, 200W지날 때, 25도 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>400 DCF-BC社-cladding removed</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -612,20 +620,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -680,13 +683,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -991,10 +1011,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.625" customWidth="1"/>
+    <col min="1" max="1" width="12.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
@@ -1003,10 +1023,11 @@
     <col min="8" max="8" width="3.625" customWidth="1"/>
     <col min="9" max="9" width="4.625" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="7.75" customWidth="1"/>
+    <col min="13" max="13" width="8.875" customWidth="1"/>
+    <col min="14" max="14" width="7.625" customWidth="1"/>
+    <col min="15" max="15" width="9.125" customWidth="1"/>
     <col min="16" max="16" width="23.875" customWidth="1"/>
     <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
@@ -1027,7 +1048,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1064,80 +1085,106 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+    <row r="2" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27">
         <v>46305</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="9">
         <v>200</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="28">
         <v>0</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="28">
         <v>0</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="28">
         <v>0</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="28">
         <v>0</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="28">
         <v>-100</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="28">
         <v>-1000</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="28">
         <v>0</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="28">
         <v>0</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="28">
         <v>0</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="28">
         <v>0</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="28">
         <v>0</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="16" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30">
+        <v>46308</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="14">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1250,198 +1297,217 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="4.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" customWidth="1"/>
     <col min="3" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="14" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="11" customWidth="1"/>
     <col min="5" max="5" width="11.125" customWidth="1"/>
     <col min="6" max="6" width="10.375" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="14" customWidth="1"/>
-    <col min="8" max="8" width="24.125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="12" customFormat="1" ht="45.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:17" s="9" customFormat="1" ht="45.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-    </row>
-    <row r="2" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+    </row>
+    <row r="2" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="15">
         <v>0.22</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E2" s="13">
         <v>9.9700000000000006</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="13">
         <v>0.17299999999999999</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="19"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="16"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="22">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="20">
         <v>46308</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="21">
         <v>0.85</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="21">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="22">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="22">
         <v>0.14000000000000001</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="21">
         <v>6.56</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="21">
         <v>0.11</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25" t="s">
+      <c r="H4" s="21"/>
+      <c r="I4" s="22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
+    <row r="5" spans="1:17" s="33" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="31">
         <v>3</v>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="32"/>
+      <c r="C5" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="33">
         <v>5.14</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="33">
         <v>0.09</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="35" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B6" s="13"/>
-      <c r="H6"/>
-      <c r="I6" s="14"/>
+    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25"/>
+      <c r="C6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="26">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="E6" s="9">
+        <v>3.3</v>
+      </c>
+      <c r="F6" s="9">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
+      <c r="B7" s="10"/>
       <c r="H7"/>
-      <c r="I7" s="14"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="13"/>
+      <c r="B8" s="10"/>
       <c r="H8"/>
-      <c r="I8" s="14"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B9" s="13"/>
+      <c r="B9" s="10"/>
       <c r="H9"/>
-      <c r="I9" s="14"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="13"/>
+      <c r="B10" s="10"/>
       <c r="H10"/>
-      <c r="I10" s="14"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="13"/>
+      <c r="B11" s="10"/>
       <c r="H11"/>
-      <c r="I11" s="14"/>
+      <c r="I11" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7798BDEB-3987-4AB4-AA9D-798FE40B0CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466B6A7A-26E5-4807-B943-93A1009DFAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="810" windowWidth="21750" windowHeight="14790" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="810" windowWidth="21750" windowHeight="14790" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
     <sheet name="Cleaver" sheetId="2" r:id="rId2"/>
     <sheet name="NA Measure" sheetId="4" r:id="rId3"/>
-    <sheet name="작성 안내" sheetId="3" r:id="rId4"/>
+    <sheet name="CPS heat load" sheetId="5" r:id="rId4"/>
+    <sheet name="작성 안내" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
   <si>
     <t>날짜</t>
   </si>
@@ -82,12 +83,6 @@
     <t>SMF-28</t>
   </si>
   <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>예시 행 - 지우고 사용</t>
-  </si>
-  <si>
     <t>클리버 모델</t>
   </si>
   <si>
@@ -97,9 +92,6 @@
     <t>Cladding 직경 (µm)</t>
   </si>
   <si>
-    <t>Coating 제거 길이 (mm)</t>
-  </si>
-  <si>
     <t>Tension (g)</t>
   </si>
   <si>
@@ -113,30 +105,6 @@
   </si>
   <si>
     <t>끝면 상태</t>
-  </si>
-  <si>
-    <t>(클리버 모델)</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>위치 1</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>Mirror</t>
   </si>
   <si>
     <t>작성 안내</t>
@@ -481,6 +449,157 @@
   </si>
   <si>
     <t>400 DCF-BC社-cladding removed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이트란</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20/400(BC社)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cleave L </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(mm)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>바트란</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>200/220</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;0.3도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPS</t>
+  </si>
+  <si>
+    <t>20/400 BC-CPS</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>부하(W)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지속시간</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>CPS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>온도</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿨링환경</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>워터</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 A~200 W</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -488,7 +607,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,6 +687,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -620,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -696,17 +829,30 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1049,7 +1195,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -1090,22 +1236,22 @@
         <v>46305</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J2" s="9">
         <v>200</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -1116,13 +1262,13 @@
         <v>17</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F3" s="28">
         <v>0</v>
@@ -1158,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="16" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
@@ -1166,16 +1312,16 @@
         <v>46308</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J4" s="14">
         <v>0</v>
@@ -1184,7 +1330,7 @@
         <v>1000</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1195,10 +1341,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" style="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -1210,36 +1356,36 @@
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -1249,41 +1395,53 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
+      <c r="A2" s="31">
+        <v>46308</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2">
+        <v>400</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>1155</v>
+      </c>
+      <c r="J2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="25"/>
+      <c r="B3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="9">
+        <v>220</v>
+      </c>
+      <c r="E3" s="9">
+        <v>9</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1309,31 +1467,31 @@
   <sheetData>
     <row r="1" spans="1:17" s="9" customFormat="1" ht="45.75" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
@@ -1352,7 +1510,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D2" s="15">
         <v>0.22</v>
@@ -1365,10 +1523,10 @@
       </c>
       <c r="G2" s="24"/>
       <c r="H2" s="15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -1387,10 +1545,10 @@
         <v>46308</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E3" s="21">
         <v>0.85</v>
@@ -1399,13 +1557,13 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -1414,7 +1572,7 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="21" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D4" s="22">
         <v>0.14000000000000001</v>
@@ -1426,38 +1584,38 @@
         <v>0.11</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H4" s="21"/>
       <c r="I4" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" s="33" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="33">
+      <c r="B5" s="31"/>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5">
         <v>5.14</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5">
         <v>0.09</v>
       </c>
-      <c r="G5" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>61</v>
+      <c r="G5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
@@ -1466,7 +1624,7 @@
       </c>
       <c r="B6" s="25"/>
       <c r="C6" s="9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D6" s="26">
         <v>6.5000000000000002E-2</v>
@@ -1478,10 +1636,10 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1517,6 +1675,150 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C410A21-8FFF-4BAF-9FA5-54C0A302D6B3}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="9" customFormat="1" ht="29.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="15">
+        <v>200</v>
+      </c>
+      <c r="E2" s="35">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2" s="13">
+        <v>39.6</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20">
+        <v>46308</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="10"/>
+      <c r="B5" s="31"/>
+      <c r="D5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" spans="1:9" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="D6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="I6" s="40"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="D7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="D9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="D10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="I10" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1526,32 +1828,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466B6A7A-26E5-4807-B943-93A1009DFAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D92AE5D-9652-495E-A02A-1434CB6C5820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="810" windowWidth="21750" windowHeight="14790" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="825" windowWidth="21720" windowHeight="14775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
   <si>
     <t>날짜</t>
   </si>
@@ -600,6 +600,51 @@
   </si>
   <si>
     <t>10 A~200 W</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잔류파워</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5.46 W</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SP31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(15A)6.1W</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -721,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -749,11 +794,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -845,13 +899,47 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1742,33 +1830,59 @@
       </c>
       <c r="I2" s="15"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
+    <row r="3" spans="1:9" s="47" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="38">
+        <v>1</v>
+      </c>
+      <c r="B3" s="39">
+        <v>46309</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="41">
+        <v>265</v>
+      </c>
+      <c r="E3" s="42">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F3" s="43">
+        <v>45.6</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="46"/>
+    </row>
+    <row r="4" spans="1:9" s="54" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48">
         <v>2</v>
       </c>
-      <c r="B3" s="20">
-        <v>46308</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B4" s="49">
+        <v>46309</v>
+      </c>
+      <c r="C4" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="22"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="22"/>
+      <c r="D4" s="51">
+        <v>310</v>
+      </c>
+      <c r="E4" s="52">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F4" s="51">
+        <v>49.3</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="51"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
@@ -1777,12 +1891,12 @@
       <c r="G5" s="11"/>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" spans="1:9" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="D6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="I6" s="40"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
@@ -1815,6 +1929,7 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/excel/splicing_parameter.xlsx
+++ b/excel/splicing_parameter.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\학계 동향\저장소 엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D92AE5D-9652-495E-A02A-1434CB6C5820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D4D53C-F960-440C-A328-D67785BFA43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="825" windowWidth="21720" windowHeight="14775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splicing" sheetId="1" r:id="rId1"/>
     <sheet name="Cleaver" sheetId="2" r:id="rId2"/>
     <sheet name="NA Measure" sheetId="4" r:id="rId3"/>
     <sheet name="CPS heat load" sheetId="5" r:id="rId4"/>
-    <sheet name="작성 안내" sheetId="3" r:id="rId5"/>
+    <sheet name="구성품정보" sheetId="6" r:id="rId5"/>
+    <sheet name="작성 안내" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="106">
   <si>
     <t>날짜</t>
   </si>
@@ -515,59 +516,452 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>쿨링환경</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 A~200 W</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>지속시간(분:초)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPS온도</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔류파워 5.46 W</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP31도(15A)6.1W</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>단일 플레이트 워터</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-20</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>장비명 / 모델</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t>사용 위치 / 용도</t>
+  </si>
+  <si>
+    <t>제조사</t>
+  </si>
+  <si>
+    <t>주요 사양</t>
+  </si>
+  <si>
+    <t>스펙시트 / 제품 링크</t>
+  </si>
+  <si>
+    <t>LW-K3010D</t>
+  </si>
+  <si>
+    <t>가변 DC 전원공급기</t>
+  </si>
+  <si>
+    <t>워터 쿨링 시스템 펌프 구동용 전원으로 사용</t>
+  </si>
+  <si>
+    <t>LONGWEI</t>
+  </si>
+  <si>
+    <t>공식 제품 페이지 기준: 출력 0–30V DC, 최대 10A, 입력 AC 110/220V, 효율 &gt;85%, 리플·노이즈 ≤10mV RMS(CV), 크기 220×160×70mm. 세부 사양은 제품 페이지/매뉴얼 기준 확인 권장.</t>
+  </si>
+  <si>
+    <t>펌프 자체가 아니라 펌프에 전원을 공급하는 DC 전원공급기. 실제 사용 전압·전류는 펌프 명판과 대조</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: https://longweielec.com/product/lw-k3010d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매뉴얼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> PDF: https://longweielec.com/download/112/lw-kd-mini-support/1532/longwei-kd-mini-smps-user-manual-en-version.pdf</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4~6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿠팡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저렴할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>지속시간</t>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대략적인</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>분</t>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구매</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:</t>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>초</t>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가이드</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <rFont val="Arial"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단가</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
       <t>)</t>
@@ -575,76 +969,27 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>CPS</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>온도</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>쿨링환경</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>워터</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>10 A~200 W</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>잔류파워</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 5.46 W</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>SP31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(15A)6.1W</t>
-    </r>
+    <t>220V 범용 전원 케이블 ( 파워케이블 )</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5천원에서 편차 심함</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>220V 파워케이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이블</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>펌프에 전압 인가</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>모름</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -652,7 +997,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -735,19 +1080,89 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -765,8 +1180,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -803,11 +1230,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFD9E1F2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -886,62 +1331,102 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1246,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
@@ -1266,7 +1751,7 @@
     <col min="17" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="60.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="60.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1804,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="9" customFormat="1">
       <c r="A2" s="27">
         <v>46305</v>
       </c>
@@ -1342,7 +1827,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="14" customFormat="1">
       <c r="A3" s="29" t="s">
         <v>16</v>
       </c>
@@ -1395,7 +1880,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="14" customFormat="1">
       <c r="A4" s="30">
         <v>46308</v>
       </c>
@@ -1430,7 +1915,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" style="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1444,7 +1929,7 @@
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,7 +1967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" s="31">
         <v>46308</v>
       </c>
@@ -1508,7 +1993,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" s="9" customFormat="1">
       <c r="A3" s="25"/>
       <c r="B3" s="9" t="s">
         <v>67</v>
@@ -1541,7 +2026,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99F6C447-90B8-47E1-98D9-F18C40565832}">
   <dimension ref="A1:Q11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" customWidth="1"/>
@@ -1553,7 +2038,7 @@
     <col min="8" max="8" width="24.125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="9" customFormat="1" ht="45.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="9" customFormat="1" ht="45.75">
       <c r="A1" s="7" t="s">
         <v>53</v>
       </c>
@@ -1590,7 +2075,7 @@
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
     </row>
-    <row r="2" spans="1:17" s="14" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="14" customFormat="1">
       <c r="A2" s="23">
         <v>1</v>
       </c>
@@ -1625,7 +2110,7 @@
       <c r="P2" s="13"/>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -1654,7 +2139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -1679,7 +2164,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1706,7 +2191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="9" customFormat="1">
       <c r="A6" s="25">
         <v>4</v>
       </c>
@@ -1730,27 +2215,27 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17">
       <c r="B7" s="10"/>
       <c r="H7"/>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17">
       <c r="B8" s="10"/>
       <c r="H8"/>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17">
       <c r="B9" s="10"/>
       <c r="H9"/>
       <c r="I9" s="11"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17">
       <c r="B10" s="10"/>
       <c r="H10"/>
       <c r="I10" s="11"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17">
       <c r="B11" s="10"/>
       <c r="H11"/>
       <c r="I11" s="11"/>
@@ -1765,166 +2250,192 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C410A21-8FFF-4BAF-9FA5-54C0A302D6B3}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="14.25" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="1" max="1" width="7" style="66" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="67" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="66" customWidth="1"/>
+    <col min="4" max="4" width="15.25" style="66" customWidth="1"/>
+    <col min="5" max="5" width="9" style="66"/>
+    <col min="6" max="6" width="14" style="66" customWidth="1"/>
+    <col min="7" max="7" width="17" style="66" customWidth="1"/>
+    <col min="8" max="8" width="19" style="66" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="66"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="9" customFormat="1" ht="29.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:9" s="37" customFormat="1" ht="33">
+      <c r="A1" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="36"/>
+    </row>
+    <row r="2" spans="1:9" s="44" customFormat="1">
+      <c r="A2" s="38">
+        <v>1</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="41">
+        <v>200</v>
+      </c>
+      <c r="E2" s="42">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F2" s="40">
+        <v>39.6</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="41"/>
+    </row>
+    <row r="3" spans="1:9" s="50" customFormat="1">
+      <c r="A3" s="45">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="48">
+        <v>265</v>
+      </c>
+      <c r="E3" s="49">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F3" s="50">
+        <v>45.6</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="51"/>
+    </row>
+    <row r="4" spans="1:9" s="55" customFormat="1">
+      <c r="A4" s="52">
+        <v>2</v>
+      </c>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="55">
+        <v>310</v>
+      </c>
+      <c r="E4" s="56">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F4" s="55">
+        <v>49.3</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="37" customFormat="1">
+      <c r="A5" s="57">
+        <v>3</v>
+      </c>
+      <c r="B5" s="58"/>
+      <c r="C5" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="60">
+        <v>500</v>
+      </c>
+      <c r="E5" s="61">
+        <v>0.125</v>
+      </c>
+      <c r="F5" s="37">
         <v>53</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="37"/>
-    </row>
-    <row r="2" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23">
+      <c r="G5" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="60"/>
+    </row>
+    <row r="6" spans="1:9" s="50" customFormat="1">
+      <c r="A6" s="45">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="B6" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="15">
-        <v>200</v>
-      </c>
-      <c r="E2" s="35">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F2" s="13">
-        <v>39.6</v>
-      </c>
-      <c r="G2" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="15"/>
-    </row>
-    <row r="3" spans="1:9" s="47" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38">
-        <v>1</v>
-      </c>
-      <c r="B3" s="39">
-        <v>46309</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="41">
+      <c r="D6" s="48">
         <v>265</v>
       </c>
-      <c r="E3" s="42">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F3" s="43">
-        <v>45.6</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="45" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="46"/>
-    </row>
-    <row r="4" spans="1:9" s="54" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48">
-        <v>2</v>
-      </c>
-      <c r="B4" s="49">
-        <v>46309</v>
-      </c>
-      <c r="C4" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="51">
-        <v>310</v>
-      </c>
-      <c r="E4" s="52">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F4" s="51">
-        <v>49.3</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="51"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="31"/>
-      <c r="D5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="I5" s="22"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="D10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="I10" s="11"/>
+      <c r="E6" s="49">
+        <v>0.125</v>
+      </c>
+      <c r="G6" s="48"/>
+      <c r="I6" s="48"/>
+    </row>
+    <row r="7" spans="1:9" s="64" customFormat="1">
+      <c r="A7" s="62"/>
+      <c r="B7" s="63"/>
+      <c r="D7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="I7" s="65"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="52"/>
+      <c r="B8" s="53"/>
+      <c r="D8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="I8" s="55"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
+      <c r="D9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="I9" s="55"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="52"/>
+      <c r="B10" s="53"/>
+      <c r="D10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="I10" s="55"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -1934,39 +2445,146 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6B13E2-3AFA-4926-BB1D-363D720406DA}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="2" max="2" width="34.125" customWidth="1"/>
+    <col min="4" max="4" width="36.75" customWidth="1"/>
+    <col min="5" max="5" width="23.125" customWidth="1"/>
+    <col min="6" max="6" width="41.375" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="8" max="8" width="45.875" customWidth="1"/>
+    <col min="9" max="9" width="65.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17.25" thickBot="1">
+      <c r="A1" s="68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="68" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="72" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="138" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A2" s="69">
+        <v>1</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="69" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="70" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
